--- a/private/ADA_web_organizer.xlsx
+++ b/private/ADA_web_organizer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iicpe\Desktop\PhD\algorithmicdesign.github.io\private\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62F0BD1-BFE0-431F-BE06-9FF385E0C183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C9C383-8586-4637-8A83-3F2CB23C2AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18105" yWindow="0" windowWidth="33600" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ADA website control" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="542">
   <si>
     <t>GRAMATICA: A general 3D shape grammar interpreter targeting the mass customization of housing</t>
   </si>
@@ -1646,9 +1646,6 @@
     <t>Advanced Engineering Informatics</t>
   </si>
   <si>
-    <t>Regras + divisião de espaços</t>
-  </si>
-  <si>
     <t>Luís Santos, Inês Caetano</t>
   </si>
   <si>
@@ -1662,6 +1659,21 @@
   </si>
   <si>
     <t>Architecture and Design for Industry 4.0</t>
+  </si>
+  <si>
+    <t>Glassbox: Execution-Aware Interactive Illustrations for Algorithmic Design</t>
+  </si>
+  <si>
+    <t>Duarte Pardal, Inês Caetano, António Leitão</t>
+  </si>
+  <si>
+    <t>Regulated Creativity: A Hierarchical Parametric Graph for Regulation-Aware Algorithmic Layout</t>
+  </si>
+  <si>
+    <t>Miguel Caroço, Tiago Farinha, Inês Caetano, António Leitão</t>
+  </si>
+  <si>
+    <t>presentation</t>
   </si>
 </sst>
 </file>
@@ -2065,9 +2077,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -2560,11 +2570,11 @@
       <c r="B14" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="26" t="s">
         <v>513</v>
       </c>
-      <c r="D14" s="52" t="s">
-        <v>291</v>
+      <c r="D14" s="26">
+        <v>2026</v>
       </c>
       <c r="E14" s="54"/>
       <c r="G14" s="12"/>
@@ -3666,9 +3676,6 @@
       <c r="C71" s="18"/>
       <c r="D71" s="13"/>
       <c r="E71" s="13"/>
-      <c r="F71" s="1" t="s">
-        <v>378</v>
-      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
@@ -3679,6 +3686,9 @@
       </c>
       <c r="D72" s="1" t="s">
         <v>531</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4088,13 +4098,13 @@
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
       <c r="B104" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C104" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>534</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>378</v>
@@ -4111,13 +4121,13 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>144</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>378</v>
@@ -4296,29 +4306,39 @@
       <c r="C120" s="11"/>
       <c r="D120" s="11"/>
       <c r="E120" s="11"/>
-      <c r="F120" s="58"/>
+      <c r="F120" s="6"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B121" s="54" t="s">
-        <v>532</v>
-      </c>
-      <c r="C121" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="D121" s="54" t="s">
+      <c r="B121" s="58" t="s">
+        <v>537</v>
+      </c>
+      <c r="C121" s="58" t="s">
+        <v>538</v>
+      </c>
+      <c r="D121" s="58" t="s">
         <v>399</v>
       </c>
-      <c r="E121" s="54"/>
+      <c r="E121" s="54" t="s">
+        <v>541</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B122" s="54"/>
-      <c r="C122" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="D122" s="54" t="s">
+      <c r="B122" s="58" t="s">
+        <v>539</v>
+      </c>
+      <c r="C122" s="58" t="s">
+        <v>540</v>
+      </c>
+      <c r="D122" s="58" t="s">
         <v>399</v>
       </c>
-      <c r="E122" s="54"/>
+      <c r="E122" s="58"/>
+      <c r="F122" s="1" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="11">
@@ -4328,7 +4348,7 @@
       <c r="C123" s="11"/>
       <c r="D123" s="11"/>
       <c r="E123" s="11"/>
-      <c r="F123" s="58"/>
+      <c r="F123" s="6"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B124" s="1" t="s">
@@ -4352,7 +4372,7 @@
       <c r="C125" s="18"/>
       <c r="D125" s="13"/>
       <c r="E125" s="13"/>
-      <c r="F125" s="58"/>
+      <c r="F125" s="6"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3"/>
